--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,11 +12,10 @@
     <sheet name="Argon e kripton (tubo chius0)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Onde quadre-riflessione" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Ampiezza e fase" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ampiezza e fase 2" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ampiezza e fase 2'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ampiezza e fase 2'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -137,9 +136,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ampiezza  (V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Δt micro (s)</t>
   </si>
   <si>
     <t xml:space="preserve">Δt (s)</t>
@@ -386,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="83">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -490,8 +486,6 @@
     <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="3" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1983,112 +1977,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="11"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="9.86328125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="10.6640625"/>
-    <col customWidth="1" min="4" max="4" width="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7">
-        <v>490</v>
-      </c>
-      <c r="B2">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="C2" s="79">
-        <v>-7.1000000000000002e-004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7">
-        <v>500</v>
-      </c>
-      <c r="B3">
-        <v>3.4399999999999999</v>
-      </c>
-      <c r="C3" s="79">
-        <v>-6.2e-004</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7">
-        <v>510</v>
-      </c>
-      <c r="B4">
-        <v>3.2200000000000002</v>
-      </c>
-      <c r="C4" s="79">
-        <v>-4.6000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>520</v>
-      </c>
-      <c r="B5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C5" s="79">
-        <v>-8.0000000000000007e-005</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7">
-        <v>534.29999999999995</v>
-      </c>
-      <c r="B6">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="C6" s="79">
-        <v>1.4999999999999999e-004</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7">
-        <v>540</v>
-      </c>
-      <c r="B7">
-        <v>1.8</v>
-      </c>
-      <c r="C7" s="79">
-        <v>1.4999999999999999e-004</v>
-      </c>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="18">
-        <v>550</v>
-      </c>
-      <c r="B8" s="59">
-        <v>1.4199999999999999</v>
-      </c>
-      <c r="C8" s="80">
-        <v>1.8000000000000001e-004</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="12.19921875"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="11.06640625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="10.265625"/>
@@ -2102,7 +1990,7 @@
         <v>36</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -2112,10 +2000,10 @@
       <c r="B2" s="53">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="C2" s="81">
+      <c r="C2" s="79">
         <v>6.4000000000000005e-004</v>
       </c>
-      <c r="D2" s="82"/>
+      <c r="D2" s="80"/>
     </row>
     <row r="3">
       <c r="A3" s="7">
@@ -2124,10 +2012,10 @@
       <c r="B3">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="C3" s="83">
+      <c r="C3" s="81">
         <v>5.2999999999999998e-004</v>
       </c>
-      <c r="D3" s="82"/>
+      <c r="D3" s="80"/>
     </row>
     <row r="4">
       <c r="A4" s="7">
@@ -2136,10 +2024,10 @@
       <c r="B4" s="30">
         <v>8.9999999999999997e-002</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="81">
         <v>4.0000000000000002e-004</v>
       </c>
-      <c r="D4" s="82"/>
+      <c r="D4" s="80"/>
     </row>
     <row r="5">
       <c r="A5" s="7">
@@ -2148,10 +2036,10 @@
       <c r="B5" s="30">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5" s="81">
         <v>4.2999999999999999e-004</v>
       </c>
-      <c r="D5" s="82"/>
+      <c r="D5" s="80"/>
     </row>
     <row r="6">
       <c r="A6" s="7">
@@ -2160,10 +2048,10 @@
       <c r="B6" s="30">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="81">
         <v>5.5000000000000003e-004</v>
       </c>
-      <c r="D6" s="82"/>
+      <c r="D6" s="80"/>
     </row>
     <row r="7">
       <c r="A7" s="7">
@@ -2172,10 +2060,10 @@
       <c r="B7" s="30">
         <v>0.27000000000000002</v>
       </c>
-      <c r="C7" s="83">
+      <c r="C7" s="81">
         <v>5.8e-004</v>
       </c>
-      <c r="D7" s="82"/>
+      <c r="D7" s="80"/>
     </row>
     <row r="8">
       <c r="A8" s="66">
@@ -2184,10 +2072,10 @@
       <c r="B8" s="30">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="81">
         <v>6.8999999999999997e-004</v>
       </c>
-      <c r="D8" s="82"/>
+      <c r="D8" s="80"/>
     </row>
     <row r="9">
       <c r="A9" s="7">
@@ -2196,10 +2084,10 @@
       <c r="B9" s="30">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="81">
         <v>9.5e-004</v>
       </c>
-      <c r="D9" s="82"/>
+      <c r="D9" s="80"/>
     </row>
     <row r="10">
       <c r="A10" s="7">
@@ -2208,10 +2096,10 @@
       <c r="B10" s="30">
         <v>0.20999999999999999</v>
       </c>
-      <c r="C10" s="83">
+      <c r="C10" s="81">
         <v>1.4400000000000001e-003</v>
       </c>
-      <c r="D10" s="82"/>
+      <c r="D10" s="80"/>
     </row>
     <row r="11">
       <c r="A11" s="7">
@@ -2220,10 +2108,10 @@
       <c r="B11" s="30">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="81">
         <v>1.7099999999999999e-003</v>
       </c>
-      <c r="D11" s="82"/>
+      <c r="D11" s="80"/>
     </row>
     <row r="12">
       <c r="A12" s="7">
@@ -2232,10 +2120,10 @@
       <c r="B12" s="30">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="81">
         <v>1.7899999999999999e-003</v>
       </c>
-      <c r="D12" s="82"/>
+      <c r="D12" s="80"/>
     </row>
     <row r="13">
       <c r="A13" s="7">
@@ -2244,10 +2132,10 @@
       <c r="B13" s="30">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="83">
+      <c r="C13" s="81">
         <v>1.8e-003</v>
       </c>
-      <c r="D13" s="82"/>
+      <c r="D13" s="80"/>
     </row>
     <row r="14" ht="14.65">
       <c r="A14" s="18">
@@ -2256,10 +2144,10 @@
       <c r="B14" s="37">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="84">
+      <c r="C14" s="82">
         <v>1.81e-003</v>
       </c>
-      <c r="D14" s="82"/>
+      <c r="D14" s="80"/>
     </row>
     <row r="18">
       <c r="B18" s="30"/>

--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Ampiezza e fase" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
   </definedNames>
   <calcPr/>
@@ -1037,10 +1037,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>190.09999999999999</v>
+        <v>190</v>
       </c>
       <c r="C2" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="7">
         <v>3.5000000000000003e-002</v>
@@ -1057,7 +1057,7 @@
         <v>381</v>
       </c>
       <c r="C3" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>5</v>
@@ -1074,7 +1074,7 @@
         <v>561</v>
       </c>
       <c r="C4" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="7">
         <v>5.0000000000000001e-003</v>
@@ -1088,10 +1088,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="9">
-        <v>760.20000000000005</v>
+        <v>760</v>
       </c>
       <c r="C5" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>7</v>
@@ -1105,10 +1105,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="14">
-        <v>935.60000000000002</v>
+        <v>936</v>
       </c>
       <c r="C6" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="16">
         <v>0.90000000000000002</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E2" s="30">
         <f>G2/G4</f>
-        <v>0.45381056300973421</v>
+        <v>0.45392998684210523</v>
       </c>
       <c r="F2" s="31">
         <f>C4-C3</f>
@@ -1259,7 +1259,7 @@
         <v>0.22</v>
       </c>
       <c r="G4" s="18">
-        <v>760.20000000000005</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" ht="14.65">
@@ -1405,19 +1405,19 @@
         <v>105</v>
       </c>
       <c r="C3" s="53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
-        <v>129.30000000000001</v>
+        <v>129</v>
       </c>
       <c r="E3" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" s="54">
         <v>151</v>
       </c>
       <c r="G3" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" s="55" t="s">
         <v>6</v>
@@ -1428,22 +1428,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="9">
-        <v>315.60000000000002</v>
+        <v>316</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" s="9">
-        <v>386.60000000000002</v>
+        <v>387</v>
       </c>
       <c r="E4" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="57">
-        <v>456.5</v>
+        <v>457</v>
       </c>
       <c r="G4" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" s="15">
         <v>0.5</v>
@@ -1454,22 +1454,22 @@
         <v>5</v>
       </c>
       <c r="B5" s="9">
-        <v>525.70000000000005</v>
+        <v>526</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="9">
-        <v>645.70000000000005</v>
+        <v>646</v>
       </c>
       <c r="E5" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="57">
         <v>760</v>
       </c>
       <c r="G5" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1477,22 +1477,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="9">
-        <v>737.39999999999998</v>
+        <v>737</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="9">
-        <v>903.5</v>
+        <v>904</v>
       </c>
       <c r="E6" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" s="57">
         <v>1063</v>
       </c>
       <c r="G6" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1500,22 +1500,22 @@
         <v>9</v>
       </c>
       <c r="B7" s="9">
-        <v>949.29999999999995</v>
+        <v>949</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9">
-        <v>1162.7</v>
+        <v>1163</v>
       </c>
       <c r="E7" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="57">
         <v>1380</v>
       </c>
       <c r="G7" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="14.65">
@@ -1523,22 +1523,22 @@
         <v>11</v>
       </c>
       <c r="B8" s="14">
-        <v>1155.4000000000001</v>
+        <v>1155</v>
       </c>
       <c r="C8" s="59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="14">
         <v>1430</v>
       </c>
       <c r="E8" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="60">
         <v>1680</v>
       </c>
       <c r="G8" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" state="visible" r:id="rId1"/>
@@ -382,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -413,7 +413,9 @@
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -423,13 +425,19 @@
     <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
@@ -1266,7 +1274,7 @@
       <c r="A5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="38">
         <v>1</v>
       </c>
       <c r="C5" s="30">
@@ -1283,7 +1291,7 @@
     </row>
     <row r="6">
       <c r="A6" s="33"/>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>2</v>
       </c>
       <c r="C6" s="30">
@@ -1295,14 +1303,14 @@
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="39">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
     </row>
     <row r="7" ht="14.65">
       <c r="A7" s="35"/>
-      <c r="B7" s="36">
+      <c r="B7" s="40">
         <v>3</v>
       </c>
       <c r="C7" s="37">
@@ -1311,16 +1319,16 @@
       <c r="D7" s="15">
         <v>5.0000000000000001e-003</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="42">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="41"/>
+      <c r="C11" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1348,19 +1356,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="42"/>
-      <c r="B1" s="43" t="s">
+      <c r="A1" s="44"/>
+      <c r="B1" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="45" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1369,25 +1377,25 @@
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="52" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="53" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="53" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="8">
@@ -1398,13 +1406,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52">
+      <c r="A3" s="54">
         <v>1</v>
       </c>
       <c r="B3" s="5">
         <v>105</v>
       </c>
-      <c r="C3" s="53">
+      <c r="C3" s="55">
         <v>5</v>
       </c>
       <c r="D3" s="5">
@@ -1413,18 +1421,18 @@
       <c r="E3" s="6">
         <v>5</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="56">
         <v>151</v>
       </c>
       <c r="G3" s="6">
         <v>5</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="57" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="56">
+      <c r="A4" s="58">
         <v>3</v>
       </c>
       <c r="B4" s="9">
@@ -1439,7 +1447,7 @@
       <c r="E4" s="10">
         <v>5</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="59">
         <v>457</v>
       </c>
       <c r="G4" s="10">
@@ -1450,7 +1458,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="56">
+      <c r="A5" s="58">
         <v>5</v>
       </c>
       <c r="B5" s="9">
@@ -1465,7 +1473,7 @@
       <c r="E5" s="10">
         <v>5</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="59">
         <v>760</v>
       </c>
       <c r="G5" s="10">
@@ -1473,7 +1481,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56">
+      <c r="A6" s="58">
         <v>7</v>
       </c>
       <c r="B6" s="9">
@@ -1488,7 +1496,7 @@
       <c r="E6" s="10">
         <v>5</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="59">
         <v>1063</v>
       </c>
       <c r="G6" s="10">
@@ -1496,7 +1504,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="56">
+      <c r="A7" s="58">
         <v>9</v>
       </c>
       <c r="B7" s="9">
@@ -1511,7 +1519,7 @@
       <c r="E7" s="10">
         <v>5</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="59">
         <v>1380</v>
       </c>
       <c r="G7" s="10">
@@ -1519,13 +1527,13 @@
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="58">
+      <c r="A8" s="60">
         <v>11</v>
       </c>
       <c r="B8" s="14">
         <v>1155</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="61">
         <v>5</v>
       </c>
       <c r="D8" s="14">
@@ -1534,7 +1542,7 @@
       <c r="E8" s="15">
         <v>5</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="62">
         <v>1680</v>
       </c>
       <c r="G8" s="15">
@@ -1567,39 +1575,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="67" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -1607,16 +1615,16 @@
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="66">
+      <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="59">
         <v>112</v>
       </c>
       <c r="C3" s="6">
         <v>5</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="69">
         <v>1.46</v>
       </c>
       <c r="E3" s="24">
@@ -1633,10 +1641,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66">
+      <c r="A4" s="68">
         <v>2</v>
       </c>
-      <c r="B4" s="57">
+      <c r="B4" s="59">
         <v>225</v>
       </c>
       <c r="C4" s="10">
@@ -1645,7 +1653,7 @@
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="70">
         <v>2</v>
       </c>
       <c r="F4" s="9">
@@ -1654,15 +1662,15 @@
       <c r="G4" s="10">
         <v>5</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="53" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66">
+      <c r="A5" s="68">
         <v>3</v>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" s="59">
         <v>338</v>
       </c>
       <c r="C5" s="10">
@@ -1671,7 +1679,7 @@
       <c r="D5" s="8">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="70">
         <v>3</v>
       </c>
       <c r="F5" s="9">
@@ -1680,15 +1688,15 @@
       <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="69">
+      <c r="H5" s="71">
         <v>295.14999999999998</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66">
+      <c r="A6" s="68">
         <v>4</v>
       </c>
-      <c r="B6" s="57">
+      <c r="B6" s="59">
         <v>450</v>
       </c>
       <c r="C6" s="10">
@@ -1697,7 +1705,7 @@
       <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="70">
         <v>4</v>
       </c>
       <c r="F6" s="9">
@@ -1706,15 +1714,15 @@
       <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="57" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="66">
-        <v>5</v>
-      </c>
-      <c r="B7" s="57">
+      <c r="A7" s="68">
+        <v>5</v>
+      </c>
+      <c r="B7" s="59">
         <v>562</v>
       </c>
       <c r="C7" s="10">
@@ -1723,7 +1731,7 @@
       <c r="D7" s="13">
         <v>0.5</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="70">
         <v>5</v>
       </c>
       <c r="F7" s="9">
@@ -1737,10 +1745,10 @@
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="70">
+      <c r="A8" s="72">
         <v>6</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="62">
         <v>676</v>
       </c>
       <c r="C8" s="15">
@@ -1749,7 +1757,7 @@
       <c r="D8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="73">
         <v>6</v>
       </c>
       <c r="F8" s="14">
@@ -1758,15 +1766,15 @@
       <c r="G8" s="15">
         <v>5</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="53" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="D9" s="72">
+      <c r="D9" s="74">
         <v>3.9947999999999997e-002</v>
       </c>
-      <c r="H9" s="72">
+      <c r="H9" s="74">
         <v>8.3797999999999997e-002</v>
       </c>
     </row>
@@ -1787,7 +1795,7 @@
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="75" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -1795,10 +1803,10 @@
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="D13" s="74">
+      <c r="D13" s="76">
         <v>1.6666666666666667</v>
       </c>
-      <c r="H13" s="74">
+      <c r="H13" s="76">
         <v>1.6666666666666667</v>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       <c r="A2" s="7">
         <v>1.5700000000000001</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C2">
@@ -1852,7 +1860,7 @@
       <c r="D2">
         <v>4.4999999999999997e-003</v>
       </c>
-      <c r="E2" s="76">
+      <c r="E2" s="78">
         <f t="shared" ref="E2:E8" si="0">AVERAGE(C2:D2)</f>
         <v>4.4999999999999997e-003</v>
       </c>
@@ -1861,7 +1869,7 @@
       <c r="A3" s="7">
         <v>1.3700000000000001</v>
       </c>
-      <c r="B3" s="75">
+      <c r="B3" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C3">
@@ -1870,7 +1878,7 @@
       <c r="D3">
         <v>3.9199999999999999e-003</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="78">
         <f t="shared" si="0"/>
         <v>3.9199999999999999e-003</v>
       </c>
@@ -1879,7 +1887,7 @@
       <c r="A4" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c r="B4" s="75">
+      <c r="B4" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C4">
@@ -1888,7 +1896,7 @@
       <c r="D4">
         <v>3.3500000000000001e-003</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="78">
         <f t="shared" si="0"/>
         <v>3.3550000000000003e-003</v>
       </c>
@@ -1897,7 +1905,7 @@
       <c r="A5" s="7">
         <v>0.96999999999999997</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C5">
@@ -1906,7 +1914,7 @@
       <c r="D5">
         <v>2.7699999999999999e-003</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="78">
         <f t="shared" si="0"/>
         <v>2.7799999999999999e-003</v>
       </c>
@@ -1915,7 +1923,7 @@
       <c r="A6" s="7">
         <v>0.77000000000000002</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C6">
@@ -1924,7 +1932,7 @@
       <c r="D6">
         <v>2.2000000000000001e-003</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="78">
         <f t="shared" si="0"/>
         <v>2.2000000000000001e-003</v>
       </c>
@@ -1933,7 +1941,7 @@
       <c r="A7" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="77">
         <v>5.0000000000000001e-003</v>
       </c>
       <c r="C7">
@@ -1942,7 +1950,7 @@
       <c r="D7">
         <v>1.6199999999999999e-003</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="78">
         <f t="shared" si="0"/>
         <v>1.6199999999999999e-003</v>
       </c>
@@ -1951,16 +1959,16 @@
       <c r="A8" s="18">
         <v>0.37</v>
       </c>
-      <c r="B8" s="77">
+      <c r="B8" s="79">
         <v>5.0000000000000001e-003</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="61">
         <v>1.0499999999999999e-003</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="61">
         <v>1.0399999999999999e-003</v>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="80">
         <f t="shared" si="0"/>
         <v>1.0449999999999999e-003</v>
       </c>
@@ -1986,24 +1994,24 @@
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="53" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="42">
+      <c r="A2" s="44">
         <v>222</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="55">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="C2" s="79">
+      <c r="C2" s="81">
         <v>6.4000000000000005e-004</v>
       </c>
-      <c r="D2" s="80"/>
+      <c r="D2" s="82"/>
     </row>
     <row r="3">
       <c r="A3" s="7">
@@ -2012,10 +2020,10 @@
       <c r="B3">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="C3" s="81">
+      <c r="C3" s="83">
         <v>5.2999999999999998e-004</v>
       </c>
-      <c r="D3" s="80"/>
+      <c r="D3" s="82"/>
     </row>
     <row r="4">
       <c r="A4" s="7">
@@ -2024,10 +2032,10 @@
       <c r="B4" s="30">
         <v>8.9999999999999997e-002</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="83">
         <v>4.0000000000000002e-004</v>
       </c>
-      <c r="D4" s="80"/>
+      <c r="D4" s="82"/>
     </row>
     <row r="5">
       <c r="A5" s="7">
@@ -2036,10 +2044,10 @@
       <c r="B5" s="30">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="83">
         <v>4.2999999999999999e-004</v>
       </c>
-      <c r="D5" s="80"/>
+      <c r="D5" s="82"/>
     </row>
     <row r="6">
       <c r="A6" s="7">
@@ -2048,10 +2056,10 @@
       <c r="B6" s="30">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="83">
         <v>5.5000000000000003e-004</v>
       </c>
-      <c r="D6" s="80"/>
+      <c r="D6" s="82"/>
     </row>
     <row r="7">
       <c r="A7" s="7">
@@ -2060,22 +2068,22 @@
       <c r="B7" s="30">
         <v>0.27000000000000002</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="83">
         <v>5.8e-004</v>
       </c>
-      <c r="D7" s="80"/>
+      <c r="D7" s="82"/>
     </row>
     <row r="8">
-      <c r="A8" s="66">
+      <c r="A8" s="68">
         <v>282</v>
       </c>
       <c r="B8" s="30">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="83">
         <v>6.8999999999999997e-004</v>
       </c>
-      <c r="D8" s="80"/>
+      <c r="D8" s="82"/>
     </row>
     <row r="9">
       <c r="A9" s="7">
@@ -2084,10 +2092,10 @@
       <c r="B9" s="30">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="83">
         <v>9.5e-004</v>
       </c>
-      <c r="D9" s="80"/>
+      <c r="D9" s="82"/>
     </row>
     <row r="10">
       <c r="A10" s="7">
@@ -2096,10 +2104,10 @@
       <c r="B10" s="30">
         <v>0.20999999999999999</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="83">
         <v>1.4400000000000001e-003</v>
       </c>
-      <c r="D10" s="80"/>
+      <c r="D10" s="82"/>
     </row>
     <row r="11">
       <c r="A11" s="7">
@@ -2108,10 +2116,10 @@
       <c r="B11" s="30">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="81">
+      <c r="C11" s="83">
         <v>1.7099999999999999e-003</v>
       </c>
-      <c r="D11" s="80"/>
+      <c r="D11" s="82"/>
     </row>
     <row r="12">
       <c r="A12" s="7">
@@ -2120,10 +2128,10 @@
       <c r="B12" s="30">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="81">
+      <c r="C12" s="83">
         <v>1.7899999999999999e-003</v>
       </c>
-      <c r="D12" s="80"/>
+      <c r="D12" s="82"/>
     </row>
     <row r="13">
       <c r="A13" s="7">
@@ -2132,10 +2140,10 @@
       <c r="B13" s="30">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="83">
         <v>1.8e-003</v>
       </c>
-      <c r="D13" s="80"/>
+      <c r="D13" s="82"/>
     </row>
     <row r="14" ht="14.65">
       <c r="A14" s="18">
@@ -2144,10 +2152,10 @@
       <c r="B14" s="37">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="82">
+      <c r="C14" s="84">
         <v>1.81e-003</v>
       </c>
-      <c r="D14" s="80"/>
+      <c r="D14" s="82"/>
     </row>
     <row r="18">
       <c r="B18" s="30"/>

--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -1,81 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Tubo risonanza/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_4EA575A1DFE3364F0B4F8B64A213E580FFB29C18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9BEDEF-29DC-4D06-877C-E87BDE14515E}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Aria (tubo aperto)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ventri e nodi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Aria (tubo semi-chiuso)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Argon e kripton (tubo chius0)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Onde quadre-riflessione" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ampiezza e fase" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
+    <sheet name="Ventri e nodi" sheetId="2" r:id="rId2"/>
+    <sheet name="Aria (tubo semi-chiuso)" sheetId="3" r:id="rId3"/>
+    <sheet name="Argon e kripton (tubo chiuso)" sheetId="4" r:id="rId4"/>
+    <sheet name="Onde quadre-riflessione" sheetId="5" r:id="rId5"/>
+    <sheet name="Ampiezza e fase" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
+    <definedName name="BF.CURVE_FIT">_xlfn.LAMBDA(_xlpm.model_expr,_xlpm.xdata,_xlpm.ydata,_xlop.guess,_xlop.bounds,_xlop.curve_fit_method, _xldudf_BOARDFLARE_EXEC("curve_fit", _xlpm.model_expr, _xlpm.xdata, _xlpm.ydata, _xludf.IF(_xlfn.ISOMITTED(_xlpm.guess), "__OMITTED__", _xlpm.guess), _xludf.IF(_xlfn.ISOMITTED(_xlpm.bounds), "__OMITTED__", _xlpm.bounds), _xludf.IF(_xlfn.ISOMITTED(_xlpm.curve_fit_method), "__OMITTED__", _xlpm.curve_fit_method)))</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
   <si>
-    <t xml:space="preserve">Frequenza (hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D diametro del tubo aperto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperatura stanza (k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza temperatura (k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza tubo (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa molare aria (kg/mol)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (kg/mol)</t>
+    <t>Frequenza (hz)</t>
+  </si>
+  <si>
+    <t>Incertezza (hz)</t>
+  </si>
+  <si>
+    <t>D diametro del tubo aperto</t>
+  </si>
+  <si>
+    <t>Temperatura stanza (k)</t>
+  </si>
+  <si>
+    <t>Incertezza (m)</t>
+  </si>
+  <si>
+    <t>Incertezza temperatura (k)</t>
+  </si>
+  <si>
+    <t>Lunghezza tubo (m)</t>
+  </si>
+  <si>
+    <t>Massa molare aria (kg/mol)</t>
+  </si>
+  <si>
+    <t>Incertezza (kg/mol)</t>
   </si>
   <si>
     <t>γ</t>
   </si>
   <si>
-    <t xml:space="preserve">R gas ideale</t>
+    <t>R gas ideale</t>
   </si>
   <si>
     <t>n=4</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">λ_n teorica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">λ_n/2 osservata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V suono (m/s)</t>
+    <t>Distanza (m)</t>
+  </si>
+  <si>
+    <t>λ_n teorica</t>
+  </si>
+  <si>
+    <t>λ_n/2 osservata</t>
+  </si>
+  <si>
+    <t>V suono (m/s)</t>
   </si>
   <si>
     <t>Ventri</t>
@@ -87,22 +126,22 @@
     <t>Media</t>
   </si>
   <si>
-    <t xml:space="preserve">λ_n sperimentale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 cm</t>
+    <t>λ_n sperimentale</t>
+  </si>
+  <si>
+    <t>80 cm</t>
+  </si>
+  <si>
+    <t>65 cm</t>
+  </si>
+  <si>
+    <t>55 cm</t>
   </si>
   <si>
     <t xml:space="preserve">Distanza dal tubo </t>
   </si>
   <si>
-    <t xml:space="preserve">1,5 cm</t>
+    <t>1,5 cm</t>
   </si>
   <si>
     <t>Argon</t>
@@ -111,40 +150,40 @@
     <t>Kripton</t>
   </si>
   <si>
-    <t xml:space="preserve">L (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T (K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa molare (kg/mol)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sx (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta T_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta T_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Δt medio (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampiezza  (V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Δt (s)</t>
+    <t>L (m)</t>
+  </si>
+  <si>
+    <t>T (K)</t>
+  </si>
+  <si>
+    <t>Massa molare (kg/mol)</t>
+  </si>
+  <si>
+    <t>x (m)</t>
+  </si>
+  <si>
+    <t>sx (m)</t>
+  </si>
+  <si>
+    <t>Delta T_1</t>
+  </si>
+  <si>
+    <t>Delta T_2</t>
+  </si>
+  <si>
+    <t>Δt medio (s)</t>
+  </si>
+  <si>
+    <t>Ampiezza  (V)</t>
+  </si>
+  <si>
+    <t>Δt (s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -155,20 +194,20 @@
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
@@ -203,22 +242,22 @@
   </fills>
   <borders count="16">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -230,28 +269,28 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -260,40 +299,40 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -302,36 +341,36 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -341,16 +380,16 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -365,139 +404,140 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="1" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="9" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="86">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="4" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -515,291 +555,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1010,20 +767,50 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="700" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2D461B2C-B42A-43C4-9A45-029F23DFB1CD}">
+  <we:reference id="WA200007447" version="1.1.6.7" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="WA200007447" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.3984375"/>
-    <col customWidth="1" min="2" max="2" width="21.59765625"/>
-    <col customWidth="1" min="3" max="5" width="22"/>
-    <col customWidth="1" min="6" max="6" width="16.265625"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
+    <col min="2" max="2" width="21.59765625" customWidth="1"/>
+    <col min="3" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1051,13 +838,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="7">
-        <v>3.5000000000000003e-002</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E2" s="8">
         <v>296.14999999999998</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1074,7 +861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1085,13 +872,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="7">
-        <v>5.0000000000000001e-003</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E4" s="13">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1108,7 +895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="14.65">
+    <row r="6" spans="1:5">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1119,13 +906,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="16">
-        <v>0.90000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="E6" s="17">
-        <v>2.8964699999999999e-002</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2.8964699999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
@@ -1133,58 +920,57 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" ht="14.65">
+    <row r="8" spans="1:5">
       <c r="D8" s="18">
-        <v>1.e-002</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="13">
-        <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="E9" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="E10" s="13">
-        <v>1.3999999999999999</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="E11" s="19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" ht="14.65">
+    <row r="12" spans="1:5">
       <c r="E12" s="20">
         <v>8.3144626180000003</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.19921875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="8.6640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="11.796875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="14"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="12.86328125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="10"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="17.265625"/>
+    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
+    <row r="1" spans="1:7">
       <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
@@ -1207,43 +993,43 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="C2" s="29">
+      <c r="B2" s="27">
+        <v>2</v>
+      </c>
+      <c r="C2" s="28">
         <v>0.34499999999999997</v>
       </c>
       <c r="D2" s="6">
-        <v>5.0000000000000001e-003</v>
-      </c>
-      <c r="E2" s="30">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E2" s="29">
         <f>G2/G4</f>
         <v>0.45392998684210523</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="30">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="31">
         <v>344.98678999999998</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34">
-        <v>2.5</v>
-      </c>
-      <c r="C3" s="30">
+    <row r="3" spans="1:7">
+      <c r="A3" s="75"/>
+      <c r="B3" s="32">
+        <v>3</v>
+      </c>
+      <c r="C3" s="29">
         <v>0.56000000000000005</v>
       </c>
       <c r="D3" s="10">
-        <v>5.0000000000000001e-003</v>
-      </c>
-      <c r="F3" s="31">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F3" s="30">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
@@ -1251,18 +1037,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="14.65">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36">
-        <v>3.5</v>
-      </c>
-      <c r="C4" s="37">
+    <row r="4" spans="1:7">
+      <c r="A4" s="76"/>
+      <c r="B4" s="33">
+        <v>4</v>
+      </c>
+      <c r="C4" s="34">
         <v>0.78800000000000003</v>
       </c>
       <c r="D4" s="15">
-        <v>5.0000000000000001e-003</v>
-      </c>
-      <c r="F4" s="31">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F4" s="30">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
@@ -1270,149 +1056,148 @@
         <v>760</v>
       </c>
     </row>
-    <row r="5" ht="14.65">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="35">
         <v>1</v>
       </c>
-      <c r="C5" s="30">
-        <v>0.23000000000000001</v>
+      <c r="C5" s="29">
+        <v>0.23</v>
       </c>
       <c r="D5" s="10">
-        <v>5.0000000000000001e-003</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="33"/>
-      <c r="B6" s="38">
+    <row r="6" spans="1:7">
+      <c r="A6" s="75"/>
+      <c r="B6" s="35">
         <v>2</v>
       </c>
-      <c r="C6" s="30">
-        <v>0.45000000000000001</v>
+      <c r="C6" s="29">
+        <v>0.45</v>
       </c>
       <c r="D6" s="10">
-        <v>5.0000000000000001e-003</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="36">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
     </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="35"/>
-      <c r="B7" s="40">
+    <row r="7" spans="1:7">
+      <c r="A7" s="76"/>
+      <c r="B7" s="37">
         <v>3</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="34">
         <v>0.67500000000000004</v>
       </c>
       <c r="D7" s="15">
-        <v>5.0000000000000001e-003</v>
-      </c>
-      <c r="E7" s="41" t="s">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E7" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="39">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" s="43"/>
+    <row r="11" spans="1:7">
+      <c r="C11" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.06640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="12.06640625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="21.33203125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="14.59765625"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="44"/>
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="1:9" ht="14.65" thickBot="1">
+      <c r="A1" s="41"/>
+      <c r="B1" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="47" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="48" t="s">
+      <c r="E1" s="78"/>
+      <c r="F1" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="49"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:9" ht="14.65" thickBot="1">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="45" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="45" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="8">
         <v>294.64999999999998</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="85" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="54">
+    <row r="3" spans="1:9">
+      <c r="A3" s="46">
         <v>1</v>
       </c>
       <c r="B3" s="5">
         <v>105</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="47">
         <v>5</v>
       </c>
       <c r="D3" s="5">
@@ -1421,18 +1206,18 @@
       <c r="E3" s="6">
         <v>5</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="48">
         <v>151</v>
       </c>
       <c r="G3" s="6">
         <v>5</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="14.65">
-      <c r="A4" s="58">
+    <row r="4" spans="1:9">
+      <c r="A4" s="50">
         <v>3</v>
       </c>
       <c r="B4" s="9">
@@ -1447,7 +1232,7 @@
       <c r="E4" s="10">
         <v>5</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="51">
         <v>457</v>
       </c>
       <c r="G4" s="10">
@@ -1457,8 +1242,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="58">
+    <row r="5" spans="1:9">
+      <c r="A5" s="50">
         <v>5</v>
       </c>
       <c r="B5" s="9">
@@ -1473,15 +1258,15 @@
       <c r="E5" s="10">
         <v>5</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="51">
         <v>760</v>
       </c>
       <c r="G5" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="58">
+    <row r="6" spans="1:9">
+      <c r="A6" s="50">
         <v>7</v>
       </c>
       <c r="B6" s="9">
@@ -1496,15 +1281,15 @@
       <c r="E6" s="10">
         <v>5</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="51">
         <v>1063</v>
       </c>
       <c r="G6" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="58">
+    <row r="7" spans="1:9">
+      <c r="A7" s="50">
         <v>9</v>
       </c>
       <c r="B7" s="9">
@@ -1519,21 +1304,21 @@
       <c r="E7" s="10">
         <v>5</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="51">
         <v>1380</v>
       </c>
       <c r="G7" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="60">
+    <row r="8" spans="1:9">
+      <c r="A8" s="52">
         <v>11</v>
       </c>
       <c r="B8" s="14">
         <v>1155</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="53">
         <v>5</v>
       </c>
       <c r="D8" s="14">
@@ -1542,7 +1327,7 @@
       <c r="E8" s="15">
         <v>5</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="54">
         <v>1680</v>
       </c>
       <c r="G8" s="15">
@@ -1555,76 +1340,76 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.06640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="21.33203125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="12.06640625"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="21.33203125"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="64" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="66" t="s">
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="84"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="67" t="s">
+      <c r="E2" s="56" t="str" cm="1">
+        <f t="array" aca="1" ref="E2" ca="1">BF.CURVE_FIT(E3:E8,F3:F9,G3:G7)</f>
+        <v>Error: Invalid input: model_expr must be a string.</v>
+      </c>
+      <c r="F2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="56" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" ht="14.65">
-      <c r="A3" s="68">
+    <row r="3" spans="1:8">
+      <c r="A3" s="57">
         <v>1</v>
       </c>
-      <c r="B3" s="59">
+      <c r="B3" s="51">
         <v>112</v>
       </c>
       <c r="C3" s="6">
         <v>5</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="58">
         <v>1.46</v>
       </c>
       <c r="E3" s="24">
@@ -1640,11 +1425,11 @@
         <v>1.454</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="68">
+    <row r="4" spans="1:8">
+      <c r="A4" s="57">
         <v>2</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="51">
         <v>225</v>
       </c>
       <c r="C4" s="10">
@@ -1653,7 +1438,7 @@
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="59">
         <v>2</v>
       </c>
       <c r="F4" s="9">
@@ -1662,15 +1447,15 @@
       <c r="G4" s="10">
         <v>5</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="45" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="68">
+    <row r="5" spans="1:8">
+      <c r="A5" s="57">
         <v>3</v>
       </c>
-      <c r="B5" s="59">
+      <c r="B5" s="51">
         <v>338</v>
       </c>
       <c r="C5" s="10">
@@ -1679,7 +1464,7 @@
       <c r="D5" s="8">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="59">
         <v>3</v>
       </c>
       <c r="F5" s="9">
@@ -1688,15 +1473,15 @@
       <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="71">
+      <c r="H5" s="60">
         <v>295.14999999999998</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="68">
+    <row r="6" spans="1:8">
+      <c r="A6" s="57">
         <v>4</v>
       </c>
-      <c r="B6" s="59">
+      <c r="B6" s="51">
         <v>450</v>
       </c>
       <c r="C6" s="10">
@@ -1705,7 +1490,7 @@
       <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="59">
         <v>4</v>
       </c>
       <c r="F6" s="9">
@@ -1714,15 +1499,15 @@
       <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="68">
-        <v>5</v>
-      </c>
-      <c r="B7" s="59">
+    <row r="7" spans="1:8">
+      <c r="A7" s="57">
+        <v>5</v>
+      </c>
+      <c r="B7" s="51">
         <v>562</v>
       </c>
       <c r="C7" s="10">
@@ -1731,7 +1516,7 @@
       <c r="D7" s="13">
         <v>0.5</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="59">
         <v>5</v>
       </c>
       <c r="F7" s="9">
@@ -1744,11 +1529,11 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="72">
+    <row r="8" spans="1:8">
+      <c r="A8" s="61">
         <v>6</v>
       </c>
-      <c r="B8" s="62">
+      <c r="B8" s="54">
         <v>676</v>
       </c>
       <c r="C8" s="15">
@@ -1757,7 +1542,7 @@
       <c r="D8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="73">
+      <c r="E8" s="62">
         <v>6</v>
       </c>
       <c r="F8" s="14">
@@ -1766,19 +1551,19 @@
       <c r="G8" s="15">
         <v>5</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="45" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="14.65">
-      <c r="D9" s="74">
-        <v>3.9947999999999997e-002</v>
-      </c>
-      <c r="H9" s="74">
-        <v>8.3797999999999997e-002</v>
-      </c>
-    </row>
-    <row r="10">
+    <row r="9" spans="1:8">
+      <c r="D9" s="63">
+        <v>3.9947999999999997E-2</v>
+      </c>
+      <c r="H9" s="63">
+        <v>8.3797999999999997E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
@@ -1786,27 +1571,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8">
       <c r="D11" s="13">
-        <v>5.0000000000000001e-004</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="H11" s="13">
-        <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="12" ht="14.65">
-      <c r="D12" s="75" t="s">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="64" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.65">
-      <c r="D13" s="76">
+    <row r="13" spans="1:8">
+      <c r="D13" s="65">
         <v>1.6666666666666667</v>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="65">
         <v>1.6666666666666667</v>
       </c>
     </row>
@@ -1815,22 +1600,21 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="10.06640625"/>
-    <col bestFit="1" customWidth="1" min="5" max="7" width="13"/>
+    <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
         <v>31</v>
       </c>
@@ -1847,331 +1631,328 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="7">
-        <v>1.5700000000000001</v>
-      </c>
-      <c r="B2" s="77">
-        <v>5.0000000000000001e-003</v>
+        <v>1.57</v>
+      </c>
+      <c r="B2" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C2">
-        <v>4.4999999999999997e-003</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="D2">
-        <v>4.4999999999999997e-003</v>
-      </c>
-      <c r="E2" s="78">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="E2" s="67">
         <f t="shared" ref="E2:E8" si="0">AVERAGE(C2:D2)</f>
-        <v>4.4999999999999997e-003</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="7">
-        <v>1.3700000000000001</v>
-      </c>
-      <c r="B3" s="77">
-        <v>5.0000000000000001e-003</v>
+        <v>1.37</v>
+      </c>
+      <c r="B3" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C3">
-        <v>3.9199999999999999e-003</v>
+        <v>3.9199999999999999E-3</v>
       </c>
       <c r="D3">
-        <v>3.9199999999999999e-003</v>
-      </c>
-      <c r="E3" s="78">
+        <v>3.9199999999999999E-3</v>
+      </c>
+      <c r="E3" s="67">
         <f t="shared" si="0"/>
-        <v>3.9199999999999999e-003</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>3.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="7">
-        <v>1.1699999999999999</v>
-      </c>
-      <c r="B4" s="77">
-        <v>5.0000000000000001e-003</v>
+        <v>1.17</v>
+      </c>
+      <c r="B4" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C4">
-        <v>3.3600000000000001e-003</v>
+        <v>3.3600000000000001E-3</v>
       </c>
       <c r="D4">
-        <v>3.3500000000000001e-003</v>
-      </c>
-      <c r="E4" s="78">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="E4" s="67">
         <f t="shared" si="0"/>
-        <v>3.3550000000000003e-003</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3.3550000000000003E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="7">
-        <v>0.96999999999999997</v>
-      </c>
-      <c r="B5" s="77">
-        <v>5.0000000000000001e-003</v>
+        <v>0.97</v>
+      </c>
+      <c r="B5" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>2.7899999999999999e-003</v>
+        <v>2.7899999999999999E-3</v>
       </c>
       <c r="D5">
-        <v>2.7699999999999999e-003</v>
-      </c>
-      <c r="E5" s="78">
+        <v>2.7699999999999999E-3</v>
+      </c>
+      <c r="E5" s="67">
         <f t="shared" si="0"/>
-        <v>2.7799999999999999e-003</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2.7799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="7">
-        <v>0.77000000000000002</v>
-      </c>
-      <c r="B6" s="77">
-        <v>5.0000000000000001e-003</v>
+        <v>0.77</v>
+      </c>
+      <c r="B6" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>2.2000000000000001e-003</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="D6">
-        <v>2.2000000000000001e-003</v>
-      </c>
-      <c r="E6" s="78">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="E6" s="67">
         <f t="shared" si="0"/>
-        <v>2.2000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7" s="77">
-        <v>5.0000000000000001e-003</v>
+      <c r="B7" s="66">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C7">
-        <v>1.6199999999999999e-003</v>
+        <v>1.6199999999999999E-3</v>
       </c>
       <c r="D7">
-        <v>1.6199999999999999e-003</v>
-      </c>
-      <c r="E7" s="78">
+        <v>1.6199999999999999E-3</v>
+      </c>
+      <c r="E7" s="67">
         <f t="shared" si="0"/>
-        <v>1.6199999999999999e-003</v>
-      </c>
-    </row>
-    <row r="8" ht="14.65">
+        <v>1.6199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="18">
         <v>0.37</v>
       </c>
-      <c r="B8" s="79">
-        <v>5.0000000000000001e-003</v>
-      </c>
-      <c r="C8" s="61">
-        <v>1.0499999999999999e-003</v>
-      </c>
-      <c r="D8" s="61">
-        <v>1.0399999999999999e-003</v>
-      </c>
-      <c r="E8" s="80">
+      <c r="B8" s="68">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C8" s="53">
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="D8" s="53">
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="E8" s="69">
         <f t="shared" si="0"/>
-        <v>1.0449999999999999e-003</v>
+        <v>1.0449999999999999E-3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.19921875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="11.06640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="10.265625"/>
+    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="45" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="44">
+    <row r="2" spans="1:4">
+      <c r="A2" s="41">
         <v>222</v>
       </c>
-      <c r="B2" s="55">
-        <v>5.0000000000000003e-002</v>
-      </c>
-      <c r="C2" s="81">
-        <v>6.4000000000000005e-004</v>
-      </c>
-      <c r="D2" s="82"/>
-    </row>
-    <row r="3">
+      <c r="B2" s="47">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="70">
+        <v>6.4000000000000005E-4</v>
+      </c>
+      <c r="D2" s="71"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="7">
         <v>232</v>
       </c>
       <c r="B3">
-        <v>7.0000000000000007e-002</v>
-      </c>
-      <c r="C3" s="83">
-        <v>5.2999999999999998e-004</v>
-      </c>
-      <c r="D3" s="82"/>
-    </row>
-    <row r="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C3" s="72">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="D3" s="71"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="7">
         <v>242</v>
       </c>
-      <c r="B4" s="30">
-        <v>8.9999999999999997e-002</v>
-      </c>
-      <c r="C4" s="83">
-        <v>4.0000000000000002e-004</v>
-      </c>
-      <c r="D4" s="82"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="29">
+        <v>0.09</v>
+      </c>
+      <c r="C4" s="72">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D4" s="71"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="7">
         <v>252</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="83">
-        <v>4.2999999999999999e-004</v>
-      </c>
-      <c r="D5" s="82"/>
-    </row>
-    <row r="6">
+      <c r="C5" s="72">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="D5" s="71"/>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="7">
         <v>262</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="83">
-        <v>5.5000000000000003e-004</v>
-      </c>
-      <c r="D6" s="82"/>
-    </row>
-    <row r="7">
+      <c r="C6" s="72">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="D6" s="71"/>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="7">
         <v>272</v>
       </c>
-      <c r="B7" s="30">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="C7" s="83">
-        <v>5.8e-004</v>
-      </c>
-      <c r="D7" s="82"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="68">
+      <c r="B7" s="29">
+        <v>0.27</v>
+      </c>
+      <c r="C7" s="72">
+        <v>5.8E-4</v>
+      </c>
+      <c r="D7" s="71"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="57">
         <v>282</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="83">
-        <v>6.8999999999999997e-004</v>
-      </c>
-      <c r="D8" s="82"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="72">
+        <v>6.8999999999999997E-4</v>
+      </c>
+      <c r="D8" s="71"/>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="7">
         <v>292</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="83">
-        <v>9.5e-004</v>
-      </c>
-      <c r="D9" s="82"/>
-    </row>
-    <row r="10">
+      <c r="C9" s="72">
+        <v>9.5E-4</v>
+      </c>
+      <c r="D9" s="71"/>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="7">
         <v>302</v>
       </c>
-      <c r="B10" s="30">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="C10" s="83">
-        <v>1.4400000000000001e-003</v>
-      </c>
-      <c r="D10" s="82"/>
-    </row>
-    <row r="11">
+      <c r="B10" s="29">
+        <v>0.21</v>
+      </c>
+      <c r="C10" s="72">
+        <v>1.4400000000000001E-3</v>
+      </c>
+      <c r="D10" s="71"/>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="7">
         <v>312</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="83">
-        <v>1.7099999999999999e-003</v>
-      </c>
-      <c r="D11" s="82"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="72">
+        <v>1.7099999999999999E-3</v>
+      </c>
+      <c r="D11" s="71"/>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="7">
         <v>322</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="83">
-        <v>1.7899999999999999e-003</v>
-      </c>
-      <c r="D12" s="82"/>
-    </row>
-    <row r="13">
+      <c r="C12" s="72">
+        <v>1.7899999999999999E-3</v>
+      </c>
+      <c r="D12" s="71"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="7">
         <v>332</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="83">
-        <v>1.8e-003</v>
-      </c>
-      <c r="D13" s="82"/>
-    </row>
-    <row r="14" ht="14.65">
+      <c r="C13" s="72">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D13" s="71"/>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="18">
         <v>342</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="34">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="84">
-        <v>1.81e-003</v>
-      </c>
-      <c r="D14" s="82"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="30"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="30"/>
+      <c r="C14" s="73">
+        <v>1.81E-3</v>
+      </c>
+      <c r="D14" s="71"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="29"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9">
-    <sortState ref="A2:C12">
+  <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
       <sortCondition ref="A1:A9"/>
     </sortState>
   </autoFilter>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -1,56 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Tubo risonanza/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_4EA575A1DFE3364F0B4F8B64A213E580FFB29C18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9BEDEF-29DC-4D06-877C-E87BDE14515E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
-    <sheet name="Ventri e nodi" sheetId="2" r:id="rId2"/>
-    <sheet name="Aria (tubo semi-chiuso)" sheetId="3" r:id="rId3"/>
-    <sheet name="Argon e kripton (tubo chiuso)" sheetId="4" r:id="rId4"/>
-    <sheet name="Onde quadre-riflessione" sheetId="5" r:id="rId5"/>
-    <sheet name="Ampiezza e fase" sheetId="6" r:id="rId6"/>
+    <sheet name="Aria (tubo aperto)" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Ventri e nodi" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Aria (tubo semi-chiuso)" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Argon e kripton (tubo chiuso)" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Onde quadre-riflessione" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Ampiezza e fase" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
-    <definedName name="BF.CURVE_FIT">_xlfn.LAMBDA(_xlpm.model_expr,_xlpm.xdata,_xlpm.ydata,_xlop.guess,_xlop.bounds,_xlop.curve_fit_method, _xldudf_BOARDFLARE_EXEC("curve_fit", _xlpm.model_expr, _xlpm.xdata, _xlpm.ydata, _xludf.IF(_xlfn.ISOMITTED(_xlpm.guess), "__OMITTED__", _xlpm.guess), _xludf.IF(_xlfn.ISOMITTED(_xlpm.bounds), "__OMITTED__", _xlpm.bounds), _xludf.IF(_xlfn.ISOMITTED(_xlpm.curve_fit_method), "__OMITTED__", _xlpm.curve_fit_method)))</definedName>
+    <definedName name="BF.CURVE_FIT">_xlfn.LAMBDA(_xlpm.model_expr,_xlpm.xdata,_xlpm.ydata,_xlop.guess,_xlop.bounds,_xlop.curve_fit_method,_XLDUDF_BOARDFLARE_EXEC("curve_fit",_xlpm.model_expr,_xlpm.xdata,_xlpm.ydata,_XLUDF.IF(_xlfn.ISOMITTED(_xlpm.guess),"__OMITTED__",_xlpm.guess),_XLUDF.IF(_xlfn.ISOMITTED(_xlpm.bounds),"__OMITTED__",_xlpm.bounds),_XLUDF.IF(_xlfn.ISOMITTED(_xlpm.curve_fit_method),"__OMITTED__",_xlpm.curve_fit_method)))</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ampiezza e fase'!$A$1:$C$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
         <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="1"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
@@ -60,88 +54,78 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>n</t>
   </si>
   <si>
-    <t>Frequenza (hz)</t>
-  </si>
-  <si>
-    <t>Incertezza (hz)</t>
-  </si>
-  <si>
-    <t>D diametro del tubo aperto</t>
-  </si>
-  <si>
-    <t>Temperatura stanza (k)</t>
-  </si>
-  <si>
-    <t>Incertezza (m)</t>
-  </si>
-  <si>
-    <t>Incertezza temperatura (k)</t>
-  </si>
-  <si>
-    <t>Lunghezza tubo (m)</t>
-  </si>
-  <si>
-    <t>Massa molare aria (kg/mol)</t>
-  </si>
-  <si>
-    <t>Incertezza (kg/mol)</t>
+    <t xml:space="preserve">Frequenza (hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D diametro del tubo aperto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperatura stanza (k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza temperatura (k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza tubo (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa molare aria (kg/mol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (kg/mol)</t>
   </si>
   <si>
     <t>γ</t>
   </si>
   <si>
-    <t>R gas ideale</t>
+    <t xml:space="preserve">R gas ideale</t>
   </si>
   <si>
     <t>n=4</t>
   </si>
   <si>
-    <t>Distanza (m)</t>
-  </si>
-  <si>
-    <t>λ_n teorica</t>
-  </si>
-  <si>
-    <t>λ_n/2 osservata</t>
-  </si>
-  <si>
-    <t>V suono (m/s)</t>
-  </si>
-  <si>
-    <t>Ventri</t>
-  </si>
-  <si>
-    <t>Nodi</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>λ_n sperimentale</t>
-  </si>
-  <si>
-    <t>80 cm</t>
-  </si>
-  <si>
-    <t>65 cm</t>
-  </si>
-  <si>
-    <t>55 cm</t>
+    <t>x(m)</t>
+  </si>
+  <si>
+    <t>sx(m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V suono (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 cm</t>
   </si>
   <si>
     <t xml:space="preserve">Distanza dal tubo </t>
   </si>
   <si>
-    <t>1,5 cm</t>
+    <t xml:space="preserve">1,5 cm</t>
   </si>
   <si>
     <t>Argon</t>
@@ -150,64 +134,64 @@
     <t>Kripton</t>
   </si>
   <si>
-    <t>L (m)</t>
-  </si>
-  <si>
-    <t>T (K)</t>
-  </si>
-  <si>
-    <t>Massa molare (kg/mol)</t>
-  </si>
-  <si>
-    <t>x (m)</t>
-  </si>
-  <si>
-    <t>sx (m)</t>
-  </si>
-  <si>
-    <t>Delta T_1</t>
-  </si>
-  <si>
-    <t>Delta T_2</t>
-  </si>
-  <si>
-    <t>Δt medio (s)</t>
-  </si>
-  <si>
-    <t>Ampiezza  (V)</t>
-  </si>
-  <si>
-    <t>Δt (s)</t>
+    <t xml:space="preserve">L (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T (K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa molare (kg/mol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sx (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta T_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta T_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δt medio (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampiezza  (V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δt (s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
@@ -240,24 +224,24 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+  <borders count="27">
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -269,28 +253,28 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -299,40 +283,40 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -341,36 +325,153 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -380,16 +481,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -404,140 +496,134 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="86">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="83">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="9" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="15" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="24" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="169" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -555,8 +641,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -767,50 +1136,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="700" row="7">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2D461B2C-B42A-43C4-9A45-029F23DFB1CD}">
-  <we:reference id="WA200007447" version="1.1.6.7" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200007447" version="1.1.6.7" store="WA200007447" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
-      <we:customFunctionIdList>
-        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
-      </we:customFunctionIdList>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.3984375" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" customWidth="1"/>
-    <col min="3" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="16.265625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="22.3984375"/>
+    <col customWidth="1" min="2" max="2" width="21.59765625"/>
+    <col customWidth="1" min="3" max="5" width="22"/>
+    <col customWidth="1" min="6" max="6" width="16.265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,7 +1166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -838,13 +1177,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="7">
-        <v>3.5000000000000003E-2</v>
+        <v>3.5000000000000003e-002</v>
       </c>
       <c r="E2" s="8">
         <v>296.14999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -861,7 +1200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -872,13 +1211,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="7">
-        <v>5.0000000000000001E-3</v>
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="E4" s="13">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -895,7 +1234,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -906,13 +1245,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="16">
-        <v>0.9</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="E6" s="17">
-        <v>2.8964699999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2.8964699999999999e-002</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
@@ -920,284 +1259,261 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="D8" s="18">
-        <v>0.01</v>
+        <v>1.e-002</v>
       </c>
       <c r="E8" s="13">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="E9" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="E10" s="13">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>1.3999999999999999</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="E11" s="19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="E12" s="20">
         <v>8.3144626180000003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.265625" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="12.75390625"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="8.6640625"/>
+    <col customWidth="1" min="3" max="3" width="9.50390625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="12.79296875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="14"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="12.86328125"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="10"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="17.265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1">
       <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="B2" s="25">
+        <v>0</v>
+      </c>
+      <c r="C2" s="26">
+        <v>5.0000000000000001e-003</v>
+      </c>
+      <c r="D2" s="27">
+        <v>344.98678999999998</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28">
+        <v>1</v>
+      </c>
+      <c r="B3" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="C3" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28">
         <v>2</v>
       </c>
-      <c r="C2" s="28">
+      <c r="B4" s="29">
+        <v>0.23000000000000001</v>
+      </c>
+      <c r="C4" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+      <c r="D4" s="32">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28">
+        <v>3</v>
+      </c>
+      <c r="B5" s="29">
         <v>0.34499999999999997</v>
       </c>
-      <c r="D2" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E2" s="29">
-        <f>G2/G4</f>
-        <v>0.45392998684210523</v>
-      </c>
-      <c r="F2" s="30">
-        <f>C4-C3</f>
-        <v>0.22799999999999998</v>
-      </c>
-      <c r="G2" s="31">
-        <v>344.98678999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="75"/>
-      <c r="B3" s="32">
-        <v>3</v>
-      </c>
-      <c r="C3" s="29">
+      <c r="C5" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28">
+        <v>4</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="C6" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28">
+        <v>5</v>
+      </c>
+      <c r="B7" s="29">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D3" s="10">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F3" s="30">
-        <f>C7-C6</f>
-        <v>0.22500000000000003</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="76"/>
-      <c r="B4" s="33">
-        <v>4</v>
-      </c>
-      <c r="C4" s="34">
+      <c r="C7" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="28">
+        <v>6</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="C8" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="28">
+        <v>7</v>
+      </c>
+      <c r="B9" s="29">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D4" s="15">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F4" s="30">
-        <f>C6-C5</f>
-        <v>0.22</v>
-      </c>
-      <c r="G4" s="18">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="35">
-        <v>1</v>
-      </c>
-      <c r="C5" s="29">
-        <v>0.23</v>
-      </c>
-      <c r="D5" s="10">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="30">
-        <f>C3-C2</f>
-        <v>0.21500000000000008</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="75"/>
-      <c r="B6" s="35">
-        <v>2</v>
-      </c>
-      <c r="C6" s="29">
-        <v>0.45</v>
-      </c>
-      <c r="D6" s="10">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="36">
-        <f>AVERAGE(F2:F5)</f>
-        <v>0.22200000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="76"/>
-      <c r="B7" s="37">
-        <v>3</v>
-      </c>
-      <c r="C7" s="34">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D7" s="15">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="39">
-        <f>2*F6</f>
-        <v>0.44400000000000006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="C11" s="40"/>
+      <c r="C9" s="30">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="33">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="C10" s="35">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="12.06640625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="12.06640625"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="21.33203125"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="14.59765625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.65" thickBot="1">
-      <c r="A1" s="41"/>
-      <c r="B1" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="81"/>
+    <row r="1" ht="14.65">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="39"/>
+      <c r="F1" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="42"/>
       <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1">
-      <c r="A2" s="42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="46" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="46" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="8">
         <v>294.64999999999998</v>
       </c>
-      <c r="I2" s="85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="46">
+      <c r="I2" s="47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="48">
         <v>1</v>
       </c>
       <c r="B3" s="5">
         <v>105</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="49">
         <v>5</v>
       </c>
       <c r="D3" s="5">
@@ -1206,18 +1522,18 @@
       <c r="E3" s="6">
         <v>5</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="50">
         <v>151</v>
       </c>
       <c r="G3" s="6">
         <v>5</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="51" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="50">
+    <row r="4">
+      <c r="A4" s="52">
         <v>3</v>
       </c>
       <c r="B4" s="9">
@@ -1232,7 +1548,7 @@
       <c r="E4" s="10">
         <v>5</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="53">
         <v>457</v>
       </c>
       <c r="G4" s="10">
@@ -1242,8 +1558,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="50">
+    <row r="5">
+      <c r="A5" s="52">
         <v>5</v>
       </c>
       <c r="B5" s="9">
@@ -1258,15 +1574,15 @@
       <c r="E5" s="10">
         <v>5</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="53">
         <v>760</v>
       </c>
       <c r="G5" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="50">
+    <row r="6">
+      <c r="A6" s="52">
         <v>7</v>
       </c>
       <c r="B6" s="9">
@@ -1281,15 +1597,15 @@
       <c r="E6" s="10">
         <v>5</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="53">
         <v>1063</v>
       </c>
       <c r="G6" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="50">
+    <row r="7">
+      <c r="A7" s="52">
         <v>9</v>
       </c>
       <c r="B7" s="9">
@@ -1304,21 +1620,21 @@
       <c r="E7" s="10">
         <v>5</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="53">
         <v>1380</v>
       </c>
       <c r="G7" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="52">
+    <row r="8">
+      <c r="A8" s="54">
         <v>11</v>
       </c>
       <c r="B8" s="14">
         <v>1155</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="55">
         <v>5</v>
       </c>
       <c r="D8" s="14">
@@ -1327,7 +1643,7 @@
       <c r="E8" s="15">
         <v>5</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="56">
         <v>1680</v>
       </c>
       <c r="G8" s="15">
@@ -1340,79 +1656,80 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="12.06640625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="21.33203125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="12.06640625"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="21.33203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="82" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="84"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="55" t="s">
+    <row r="1">
+      <c r="A1" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="56" t="str" cm="1">
-        <f t="array" aca="1" ref="E2" ca="1">BF.CURVE_FIT(E3:E8,F3:F9,G3:G7)</f>
-        <v>Error: Invalid input: model_expr must be a string.</v>
-      </c>
-      <c r="F2" s="56" t="s">
+      <c r="D2" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="61" t="str" cm="1">
+        <f t="array" ref="E2" ca="1">BF.CURVE_FIT(E3:E8,F3:F9,G3:G7)</f>
+        <v xml:space="preserve">Error: Invalid input: model_expr must be a string.</v>
+      </c>
+      <c r="F2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="61" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="57">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62">
         <v>1</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="53">
         <v>112</v>
       </c>
       <c r="C3" s="6">
         <v>5</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="63">
         <v>1.46</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="64">
         <v>1</v>
       </c>
       <c r="F3" s="5">
@@ -1425,20 +1742,20 @@
         <v>1.454</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="57">
+    <row r="4">
+      <c r="A4" s="62">
         <v>2</v>
       </c>
-      <c r="B4" s="51">
+      <c r="B4" s="53">
         <v>225</v>
       </c>
       <c r="C4" s="10">
         <v>5</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="59">
+        <v>24</v>
+      </c>
+      <c r="E4" s="65">
         <v>2</v>
       </c>
       <c r="F4" s="9">
@@ -1447,15 +1764,15 @@
       <c r="G4" s="10">
         <v>5</v>
       </c>
-      <c r="H4" s="45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="57">
+      <c r="H4" s="46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="62">
         <v>3</v>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="53">
         <v>338</v>
       </c>
       <c r="C5" s="10">
@@ -1464,7 +1781,7 @@
       <c r="D5" s="8">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="65">
         <v>3</v>
       </c>
       <c r="F5" s="9">
@@ -1473,15 +1790,15 @@
       <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="66">
         <v>295.14999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="57">
+    <row r="6">
+      <c r="A6" s="62">
         <v>4</v>
       </c>
-      <c r="B6" s="51">
+      <c r="B6" s="53">
         <v>450</v>
       </c>
       <c r="C6" s="10">
@@ -1490,7 +1807,7 @@
       <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="65">
         <v>4</v>
       </c>
       <c r="F6" s="9">
@@ -1499,15 +1816,15 @@
       <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="51" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="57">
-        <v>5</v>
-      </c>
-      <c r="B7" s="51">
+    <row r="7">
+      <c r="A7" s="62">
+        <v>5</v>
+      </c>
+      <c r="B7" s="53">
         <v>562</v>
       </c>
       <c r="C7" s="10">
@@ -1516,7 +1833,7 @@
       <c r="D7" s="13">
         <v>0.5</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="65">
         <v>5</v>
       </c>
       <c r="F7" s="9">
@@ -1529,20 +1846,20 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="61">
+    <row r="8">
+      <c r="A8" s="67">
         <v>6</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="56">
         <v>676</v>
       </c>
       <c r="C8" s="15">
         <v>5</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="62">
+        <v>25</v>
+      </c>
+      <c r="E8" s="68">
         <v>6</v>
       </c>
       <c r="F8" s="14">
@@ -1551,19 +1868,19 @@
       <c r="G8" s="15">
         <v>5</v>
       </c>
-      <c r="H8" s="45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="D9" s="63">
-        <v>3.9947999999999997E-2</v>
-      </c>
-      <c r="H9" s="63">
-        <v>8.3797999999999997E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H8" s="46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="69">
+        <v>3.9947999999999997e-002</v>
+      </c>
+      <c r="H9" s="69">
+        <v>8.3797999999999997e-002</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
@@ -1571,27 +1888,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11">
       <c r="D11" s="13">
-        <v>5.0000000000000001E-4</v>
+        <v>5.0000000000000001e-004</v>
       </c>
       <c r="H11" s="13">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="D12" s="64" t="s">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="70" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="D13" s="65">
+    <row r="13">
+      <c r="D13" s="71">
         <v>1.6666666666666667</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="71">
         <v>1.6666666666666667</v>
       </c>
     </row>
@@ -1600,359 +1917,363 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="10.06640625"/>
+    <col bestFit="1" customWidth="1" min="5" max="7" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    <row r="1">
+      <c r="A1" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="7">
-        <v>1.57</v>
-      </c>
-      <c r="B2" s="66">
-        <v>5.0000000000000001E-3</v>
+        <v>1.5700000000000001</v>
+      </c>
+      <c r="B2" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C2">
-        <v>4.4999999999999997E-3</v>
+        <v>4.4999999999999997e-003</v>
       </c>
       <c r="D2">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="E2" s="67">
+        <v>4.4999999999999997e-003</v>
+      </c>
+      <c r="E2" s="75">
         <f t="shared" ref="E2:E8" si="0">AVERAGE(C2:D2)</f>
-        <v>4.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>4.4999999999999997e-003</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="7">
-        <v>1.37</v>
-      </c>
-      <c r="B3" s="66">
-        <v>5.0000000000000001E-3</v>
+        <v>1.3700000000000001</v>
+      </c>
+      <c r="B3" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C3">
-        <v>3.9199999999999999E-3</v>
+        <v>3.9199999999999999e-003</v>
       </c>
       <c r="D3">
-        <v>3.9199999999999999E-3</v>
-      </c>
-      <c r="E3" s="67">
+        <v>3.9199999999999999e-003</v>
+      </c>
+      <c r="E3" s="75">
         <f t="shared" si="0"/>
-        <v>3.9199999999999999E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>3.9199999999999999e-003</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="7">
-        <v>1.17</v>
-      </c>
-      <c r="B4" s="66">
-        <v>5.0000000000000001E-3</v>
+        <v>1.1699999999999999</v>
+      </c>
+      <c r="B4" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C4">
-        <v>3.3600000000000001E-3</v>
+        <v>3.3600000000000001e-003</v>
       </c>
       <c r="D4">
-        <v>3.3500000000000001E-3</v>
-      </c>
-      <c r="E4" s="67">
+        <v>3.3500000000000001e-003</v>
+      </c>
+      <c r="E4" s="75">
         <f t="shared" si="0"/>
-        <v>3.3550000000000003E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>3.3550000000000003e-003</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="B5" s="66">
-        <v>5.0000000000000001E-3</v>
+        <v>0.96999999999999997</v>
+      </c>
+      <c r="B5" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C5">
-        <v>2.7899999999999999E-3</v>
+        <v>2.7899999999999999e-003</v>
       </c>
       <c r="D5">
-        <v>2.7699999999999999E-3</v>
-      </c>
-      <c r="E5" s="67">
+        <v>2.7699999999999999e-003</v>
+      </c>
+      <c r="E5" s="75">
         <f t="shared" si="0"/>
-        <v>2.7799999999999999E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>2.7799999999999999e-003</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="7">
-        <v>0.77</v>
-      </c>
-      <c r="B6" s="66">
-        <v>5.0000000000000001E-3</v>
+        <v>0.77000000000000002</v>
+      </c>
+      <c r="B6" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C6">
-        <v>2.2000000000000001E-3</v>
+        <v>2.2000000000000001e-003</v>
       </c>
       <c r="D6">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="E6" s="67">
+        <v>2.2000000000000001e-003</v>
+      </c>
+      <c r="E6" s="75">
         <f t="shared" si="0"/>
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2.2000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7" s="66">
-        <v>5.0000000000000001E-3</v>
+      <c r="B7" s="74">
+        <v>5.0000000000000001e-003</v>
       </c>
       <c r="C7">
-        <v>1.6199999999999999E-3</v>
+        <v>1.6199999999999999e-003</v>
       </c>
       <c r="D7">
-        <v>1.6199999999999999E-3</v>
-      </c>
-      <c r="E7" s="67">
+        <v>1.6199999999999999e-003</v>
+      </c>
+      <c r="E7" s="75">
         <f t="shared" si="0"/>
-        <v>1.6199999999999999E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.6199999999999999e-003</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="18">
         <v>0.37</v>
       </c>
-      <c r="B8" s="68">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C8" s="53">
-        <v>1.0499999999999999E-3</v>
-      </c>
-      <c r="D8" s="53">
-        <v>1.0399999999999999E-3</v>
-      </c>
-      <c r="E8" s="69">
+      <c r="B8" s="76">
+        <v>5.0000000000000001e-003</v>
+      </c>
+      <c r="C8" s="55">
+        <v>1.0499999999999999e-003</v>
+      </c>
+      <c r="D8" s="55">
+        <v>1.0399999999999999e-003</v>
+      </c>
+      <c r="E8" s="77">
         <f t="shared" si="0"/>
-        <v>1.0449999999999999E-3</v>
+        <v>1.0449999999999999e-003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="12.19921875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="11.06640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="10.265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="41">
+      <c r="B1" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="37">
         <v>222</v>
       </c>
-      <c r="B2" s="47">
-        <v>0.05</v>
-      </c>
-      <c r="C2" s="70">
-        <v>6.4000000000000005E-4</v>
-      </c>
-      <c r="D2" s="71"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="B2" s="49">
+        <v>5.0000000000000003e-002</v>
+      </c>
+      <c r="C2" s="78">
+        <v>6.4000000000000005e-004</v>
+      </c>
+      <c r="D2" s="79"/>
+    </row>
+    <row r="3">
       <c r="A3" s="7">
         <v>232</v>
       </c>
       <c r="B3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C3" s="72">
-        <v>5.2999999999999998E-4</v>
-      </c>
-      <c r="D3" s="71"/>
-    </row>
-    <row r="4" spans="1:4">
+        <v>7.0000000000000007e-002</v>
+      </c>
+      <c r="C3" s="80">
+        <v>5.2999999999999998e-004</v>
+      </c>
+      <c r="D3" s="79"/>
+    </row>
+    <row r="4">
       <c r="A4" s="7">
         <v>242</v>
       </c>
       <c r="B4" s="29">
-        <v>0.09</v>
-      </c>
-      <c r="C4" s="72">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="D4" s="71"/>
-    </row>
-    <row r="5" spans="1:4">
+        <v>8.9999999999999997e-002</v>
+      </c>
+      <c r="C4" s="80">
+        <v>4.0000000000000002e-004</v>
+      </c>
+      <c r="D4" s="79"/>
+    </row>
+    <row r="5">
       <c r="A5" s="7">
         <v>252</v>
       </c>
       <c r="B5" s="29">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="72">
-        <v>4.2999999999999999E-4</v>
-      </c>
-      <c r="D5" s="71"/>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="C5" s="80">
+        <v>4.2999999999999999e-004</v>
+      </c>
+      <c r="D5" s="79"/>
+    </row>
+    <row r="6">
       <c r="A6" s="7">
         <v>262</v>
       </c>
       <c r="B6" s="29">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="72">
-        <v>5.5000000000000003E-4</v>
-      </c>
-      <c r="D6" s="71"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="80">
+        <v>5.5000000000000003e-004</v>
+      </c>
+      <c r="D6" s="79"/>
+    </row>
+    <row r="7">
       <c r="A7" s="7">
         <v>272</v>
       </c>
       <c r="B7" s="29">
-        <v>0.27</v>
-      </c>
-      <c r="C7" s="72">
-        <v>5.8E-4</v>
-      </c>
-      <c r="D7" s="71"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="57">
+        <v>0.27000000000000002</v>
+      </c>
+      <c r="C7" s="80">
+        <v>5.8e-004</v>
+      </c>
+      <c r="D7" s="79"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="62">
         <v>282</v>
       </c>
       <c r="B8" s="29">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="72">
-        <v>6.8999999999999997E-4</v>
-      </c>
-      <c r="D8" s="71"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="C8" s="80">
+        <v>6.8999999999999997e-004</v>
+      </c>
+      <c r="D8" s="79"/>
+    </row>
+    <row r="9">
       <c r="A9" s="7">
         <v>292</v>
       </c>
       <c r="B9" s="29">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="72">
-        <v>9.5E-4</v>
-      </c>
-      <c r="D9" s="71"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="C9" s="80">
+        <v>9.5e-004</v>
+      </c>
+      <c r="D9" s="79"/>
+    </row>
+    <row r="10">
       <c r="A10" s="7">
         <v>302</v>
       </c>
       <c r="B10" s="29">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="72">
-        <v>1.4400000000000001E-3</v>
-      </c>
-      <c r="D10" s="71"/>
-    </row>
-    <row r="11" spans="1:4">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="C10" s="80">
+        <v>1.4400000000000001e-003</v>
+      </c>
+      <c r="D10" s="79"/>
+    </row>
+    <row r="11">
       <c r="A11" s="7">
         <v>312</v>
       </c>
       <c r="B11" s="29">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="72">
-        <v>1.7099999999999999E-3</v>
-      </c>
-      <c r="D11" s="71"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="C11" s="80">
+        <v>1.7099999999999999e-003</v>
+      </c>
+      <c r="D11" s="79"/>
+    </row>
+    <row r="12">
       <c r="A12" s="7">
         <v>322</v>
       </c>
       <c r="B12" s="29">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="72">
-        <v>1.7899999999999999E-3</v>
-      </c>
-      <c r="D12" s="71"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="C12" s="80">
+        <v>1.7899999999999999e-003</v>
+      </c>
+      <c r="D12" s="79"/>
+    </row>
+    <row r="13">
       <c r="A13" s="7">
         <v>332</v>
       </c>
       <c r="B13" s="29">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="72">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D13" s="71"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="C13" s="80">
+        <v>1.8e-003</v>
+      </c>
+      <c r="D13" s="79"/>
+    </row>
+    <row r="14">
       <c r="A14" s="18">
         <v>342</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="81">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="73">
-        <v>1.81E-3</v>
-      </c>
-      <c r="D14" s="71"/>
-    </row>
-    <row r="18" spans="2:2">
+      <c r="C14" s="82">
+        <v>1.81e-003</v>
+      </c>
+      <c r="D14" s="79"/>
+    </row>
+    <row r="18">
       <c r="B18" s="29"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19">
       <c r="B19" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+  <autoFilter ref="A1:C9">
+    <sortState ref="A2:C12">
       <sortCondition ref="A1:A9"/>
     </sortState>
   </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Tubo risonanza/Tubo risonanza.xlsx
+++ b/Tubo risonanza/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Tubo risonanza/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_4EA575A1DFE3364F0B4F8B64A213E580FFB29C18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9BEDEF-29DC-4D06-877C-E87BDE14515E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_4EA575A1DFE3364F0B4F8B64A213E580FFB29C18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA1CB9CC-BC71-4AFC-A393-047A1797CEB9}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1688" yWindow="2670" windowWidth="16200" windowHeight="9307" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -504,6 +504,16 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,16 +538,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -789,6 +789,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions val="1"/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
@@ -994,7 +997,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="78" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="27">
@@ -1019,7 +1022,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="75"/>
+      <c r="A3" s="79"/>
       <c r="B3" s="32">
         <v>3</v>
       </c>
@@ -1038,7 +1041,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="76"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="33">
         <v>4</v>
       </c>
@@ -1057,7 +1060,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="78" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="35">
@@ -1076,7 +1079,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="75"/>
+      <c r="A6" s="79"/>
       <c r="B6" s="35">
         <v>2</v>
       </c>
@@ -1095,7 +1098,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="76"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="37">
         <v>3</v>
       </c>
@@ -1142,18 +1145,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.65" thickBot="1">
       <c r="A1" s="41"/>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="79" t="s">
+      <c r="C1" s="82"/>
+      <c r="D1" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1186,7 +1189,7 @@
       <c r="H2" s="8">
         <v>294.64999999999998</v>
       </c>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="74" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1359,18 +1362,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="84"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="77"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="55" t="s">
